--- a/artfynd/Blåtjärnen artfynd.xlsx
+++ b/artfynd/Blåtjärnen artfynd.xlsx
@@ -903,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101283513</v>
+        <v>104441837</v>
       </c>
       <c r="B4" t="n">
-        <v>80432</v>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,38 +914,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blåtjärn, Mpd</t>
+          <t>Blåtjärn, söder om, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501116</v>
+        <v>501437</v>
       </c>
       <c r="R4" t="n">
-        <v>6914627</v>
+        <v>6914890</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,12 +968,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -985,48 +984,65 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>stavatallskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal tallåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>101283510</v>
+        <v>101283513</v>
       </c>
       <c r="B5" t="n">
-        <v>80461</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1099,10 +1115,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>53489749</v>
+        <v>101283510</v>
       </c>
       <c r="B6" t="n">
-        <v>57141</v>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1110,41 +1126,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Avaflon, Mpd</t>
+          <t>Blåtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501679</v>
+        <v>501116</v>
       </c>
       <c r="R6" t="n">
-        <v>6914725</v>
+        <v>6914627</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1168,12 +1181,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1997-09-20</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1997-09-20</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,79 +1197,68 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>SCA Skogsmark</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Caroline Westerlund</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Rydkvist</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96090594</v>
+        <v>53489749</v>
       </c>
       <c r="B7" t="n">
-        <v>99118</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Avaflon, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501289</v>
+        <v>501679</v>
       </c>
       <c r="R7" t="n">
-        <v>6914698</v>
+        <v>6914725</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,12 +1282,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>1997-09-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-09-13</t>
+          <t>1997-09-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1296,66 +1298,73 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>SCA Skogsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Caroline Westerlund</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Tomas Rydkvist</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96095720</v>
+        <v>104441836</v>
       </c>
       <c r="B8" t="n">
-        <v>99118</v>
+        <v>5495</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>101410</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Blåtjärn, söder om, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501377</v>
+        <v>501290</v>
       </c>
       <c r="R8" t="n">
-        <v>6914704</v>
+        <v>6914931</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1379,12 +1388,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1395,23 +1404,40 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>stavatallskog, naturskog med gamla tallar spridda</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>1 substratenheter # ca 250-årig tall</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96095896</v>
+        <v>96090594</v>
       </c>
       <c r="B9" t="n">
         <v>99118</v>
@@ -1440,7 +1466,11 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1448,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501424</v>
+        <v>501289</v>
       </c>
       <c r="R9" t="n">
-        <v>6914735</v>
+        <v>6914698</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1478,12 +1508,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2021-09-13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,7 +1540,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99036744</v>
+        <v>96094228</v>
       </c>
       <c r="B10" t="n">
         <v>99118</v>
@@ -1539,23 +1569,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Blåtjärnen, 400 m S om, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501377</v>
+        <v>501315</v>
       </c>
       <c r="R10" t="n">
-        <v>6914702</v>
+        <v>6914959</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,11 +1605,6 @@
           <t>Haverö</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Y-Ång-0112</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
           <t>2021-09-14</t>
@@ -1598,14 +1621,8 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1618,15 +1635,11 @@
           <t>Agneta Toomingas</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>101283482</v>
+        <v>96095720</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1659,14 +1672,14 @@
       <c r="L11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Blåtjärn, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501203</v>
+        <v>501377</v>
       </c>
       <c r="R11" t="n">
-        <v>6914552</v>
+        <v>6914704</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1693,12 +1706,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1713,19 +1726,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>101283491</v>
+        <v>96095896</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1758,14 +1771,14 @@
       <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Blåtjärn, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501202</v>
+        <v>501424</v>
       </c>
       <c r="R12" t="n">
-        <v>6914547</v>
+        <v>6914735</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1792,12 +1805,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,19 +1825,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101283522</v>
+        <v>96096104</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1857,14 +1870,14 @@
       <c r="L13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Blåtjärn, Mpd</t>
+          <t>Ånge, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501124</v>
+        <v>501315</v>
       </c>
       <c r="R13" t="n">
-        <v>6914634</v>
+        <v>6914983</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1891,12 +1904,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1911,64 +1924,64 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103456751</v>
+        <v>99036744</v>
       </c>
       <c r="B14" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Blåtjärn, söder om, Mpd</t>
+          <t>Blåtjärnen, 400 m S om, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501410</v>
+        <v>501377</v>
       </c>
       <c r="R14" t="n">
-        <v>6914760</v>
+        <v>6914702</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1990,14 +2003,19 @@
           <t>Haverö</t>
         </is>
       </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Y-Ång-0112</t>
+        </is>
+      </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2006,71 +2024,80 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>stavatallskog, naturskog i brant och blockig sydsluttning</t>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Agneta Toomingas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104441837</v>
+        <v>99037002</v>
       </c>
       <c r="B15" t="n">
-        <v>78993</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Blåtjärn, söder om, Mpd</t>
+          <t>Blåtjärnen, 150 m S om, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501437</v>
+        <v>501314</v>
       </c>
       <c r="R15" t="n">
-        <v>6914890</v>
+        <v>6914983</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2092,14 +2119,19 @@
           <t>Haverö</t>
         </is>
       </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Y-Ång-0113</t>
+        </is>
+      </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2108,83 +2140,78 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>stavatallskog</t>
-        </is>
-      </c>
-      <c r="AN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>1 substratenheter # gammal tallåga</t>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Agneta Toomingas</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>104441836</v>
+        <v>101283482</v>
       </c>
       <c r="B16" t="n">
-        <v>5495</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>101410</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Blåtjärn, söder om, Mpd</t>
+          <t>Blåtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501290</v>
+        <v>501203</v>
       </c>
       <c r="R16" t="n">
-        <v>6914931</v>
+        <v>6914552</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2208,12 +2235,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2224,40 +2251,23 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>stavatallskog, naturskog med gamla tallar spridda</t>
-        </is>
-      </c>
-      <c r="AN16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>1 substratenheter # ca 250-årig tall</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96094228</v>
+        <v>101283491</v>
       </c>
       <c r="B17" t="n">
         <v>99118</v>
@@ -2290,14 +2300,14 @@
       <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Blåtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501315</v>
+        <v>501202</v>
       </c>
       <c r="R17" t="n">
-        <v>6914959</v>
+        <v>6914547</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2324,12 +2334,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2344,19 +2354,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96096104</v>
+        <v>101283522</v>
       </c>
       <c r="B18" t="n">
         <v>99118</v>
@@ -2389,14 +2399,14 @@
       <c r="L18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ånge, Mpd</t>
+          <t>Blåtjärn, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501315</v>
+        <v>501124</v>
       </c>
       <c r="R18" t="n">
-        <v>6914983</v>
+        <v>6914634</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2423,12 +2433,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2443,64 +2453,64 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>99037002</v>
+        <v>103456751</v>
       </c>
       <c r="B19" t="n">
-        <v>99118</v>
+        <v>106244</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Blåtjärnen, 150 m S om, Mpd</t>
+          <t>Blåtjärn, söder om, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501314</v>
+        <v>501410</v>
       </c>
       <c r="R19" t="n">
-        <v>6914983</v>
+        <v>6914760</v>
       </c>
       <c r="S19" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2522,19 +2532,14 @@
           <t>Haverö</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Y-Ång-0113</t>
-        </is>
-      </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2021-09-14</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2543,31 +2548,26 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>stavatallskog, naturskog i brant och blockig sydsluttning</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Agneta Toomingas</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
